--- a/samples/outputs/HPE_Deal_9500000002_v1_NoCalculation.xlsx
+++ b/samples/outputs/HPE_Deal_9500000002_v1_NoCalculation.xlsx
@@ -112,9 +112,6 @@
   </x:si>
   <x:si>
     <x:t>Aruba 6200M 48G CL4 PoE 4SFP+ Sw</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Max Qty: 5</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -612,25 +609,19 @@
       <x:c r="I3" s="0">
         <x:v>5128.5</x:v>
       </x:c>
-      <x:c r="R3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="W3" s="0">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" spans="1:27">
       <x:c r="A4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>5</x:v>
@@ -640,26 +631,20 @@
       </x:c>
       <x:c r="I4" s="0">
         <x:v>638</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="W4" s="0">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:27">
       <x:c r="A5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>5</x:v>
@@ -669,26 +654,20 @@
       </x:c>
       <x:c r="I5" s="0">
         <x:v>0.0001</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="W5" s="0">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:27">
       <x:c r="A6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>5</x:v>
@@ -698,20 +677,14 @@
       </x:c>
       <x:c r="I6" s="0">
         <x:v>276.5</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="W6" s="0">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:27">
       <x:c r="B7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>42</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
